--- a/technology_surveys/017_enterprise_llm_evaluation_survey--technology_surveys.xlsx
+++ b/technology_surveys/017_enterprise_llm_evaluation_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>provider_id</t>
+          <t>select_provider</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>select_provider</t>
+          <t>Select a Provider</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>provider</t>
+          <t>selected_provider</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>selected_provider</t>
+          <t>Selected Provider</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>performance_rating</t>
+          <t>Performance Rating</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>adoption_rating</t>
+          <t>Adoption Rating</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>satisfaction_rating</t>
+          <t>Satisfaction Rating</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>recommendation</t>
+          <t>would_recommend</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>would_recommend</t>
+          <t>Would Recommend</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_selection</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category Selection</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_selection</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description Selection</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>tool_selection</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Tool Selection</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>tool_selection2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Output File</t>
+          <t>Tool Selection 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>tool_selection3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Tool Selection 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>tool_selection_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Tool Selection (4)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>tool_selection4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Tool Selection4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,62 +1026,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>tool_selection5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Tool Selection 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +1052,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +1080,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>provider_id_choices</t>
+          <t>select_provider_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1097,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>provider_id_choices</t>
+          <t>select_provider_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1194,17 +1148,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>adoption_rating_choices</t>
+          <t>performance_rating_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1216,418 +1170,401 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>satisfaction_rating_choices</t>
+          <t>adoption_rating_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>satisfaction_rating_choices</t>
+          <t>adoption_rating_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>recommendation_choices</t>
+          <t>satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>recommendation_choices</t>
+          <t>satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>would_recommend_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>description_choices</t>
+          <t>would_recommend_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>description_choices</t>
+          <t>category_selection_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>category_selection_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>description_selection_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>output_file_choices</t>
+          <t>description_selection_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>output_file_choices</t>
+          <t>tool_selection_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection4_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection4_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection5_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>tool_selection5_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
